--- a/latex/tabs/recommendations_4_2.xlsx
+++ b/latex/tabs/recommendations_4_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,11 +486,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -509,13 +509,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[-0.02671872 -0.12006385 -0.04660228  0.0841307   0.03919848  0.03988924
- -0.00030008 -0.05717535 -0.13684878  0.01067932]</t>
+          <t>[ 0.0465306   0.02974993  0.06680171 -0.01305856 -0.12526795  0.00077788
+  0.02021903 -0.0903551   0.00950286 -0.13158965]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
@@ -525,17 +526,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
@@ -552,13 +549,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[-0.02671872 -0.12006385 -0.04660228  0.0841307   0.03919848  0.03988924
- -0.00030008 -0.05717535 -0.13684878  0.01067932]</t>
+          <t>[ 0.0465306   0.02974993  0.06680171 -0.01305856 -0.12526795  0.00077788
+  0.02021903 -0.0903551   0.00950286 -0.13158965]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
@@ -572,7 +570,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -591,19 +589,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[-0.02671872 -0.12006385 -0.04660228  0.0841307   0.03919848  0.03988924
- -0.00030008 -0.05717535 -0.13684878  0.01067932]</t>
+          <t>[ 0.0465306   0.02974993  0.06680171 -0.01305856 -0.12526795  0.00077788
+  0.02021903 -0.0903551   0.00950286 -0.13158965]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -611,13 +610,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -626,23 +629,24 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4.413195061932108</v>
+        <v>1.875335040596766</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[-0.0202613  -0.04456411  0.01763561  0.03468722 -0.01282106 -0.07931451
- -0.06390321  0.07865211  0.08622597 -0.06775538]</t>
+          <t>[ 0.0465306   0.02974993  0.06680171 -0.01305856 -0.12526795  0.00077788
+  0.02021903 -0.0903551   0.00950286 -0.13158965]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,17 +654,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -669,17 +669,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.413195061932108</v>
+        <v>1.875335040596766</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[-0.0202613  -0.04456411  0.01763561  0.03468722 -0.01282106 -0.07931451
- -0.06390321  0.07865211  0.08622597 -0.06775538]</t>
+          <t>[ 0.0465306   0.02974993  0.06680171 -0.01305856 -0.12526795  0.00077788
+  0.02021903 -0.0903551   0.00950286 -0.13158965]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
@@ -693,7 +694,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -712,19 +713,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[-0.0202613  -0.04456411  0.01763561  0.03468722 -0.01282106 -0.07931451
- -0.06390321  0.07865211  0.08622597 -0.06775538]</t>
+          <t>[ 0.08872841 -0.01320167  0.03549391  0.00948584  0.09199315 -0.01354269
+ -0.05072576  0.01345282  0.02929437 -0.10438111]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -732,13 +734,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -747,23 +749,24 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.873519599613941</v>
+        <v>4.413195061932108</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[ 0.01754377  0.0564666  -0.02013848  0.01368242  0.05141961 -0.03902093
-  0.04681401  0.11661595  0.02467349  0.07719385]</t>
+          <t>[ 0.08872841 -0.01320167  0.03549391  0.00948584  0.09199315 -0.01354269
+ -0.05072576  0.01345282  0.02929437 -0.10438111]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -771,17 +774,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -790,31 +793,32 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.873519599613941</v>
+        <v>4.413195061932108</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[ 0.01754377  0.0564666  -0.02013848  0.01368242  0.05141961 -0.03902093
-  0.04681401  0.11661595  0.02467349  0.07719385]</t>
+          <t>[ 0.08872841 -0.01320167  0.03549391  0.00948584  0.09199315 -0.01354269
+ -0.05072576  0.01345282  0.02929437 -0.10438111]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
@@ -824,7 +828,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -833,41 +837,38 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.873519599613941</v>
+        <v>4.413195061932108</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[ 0.01754377  0.0564666  -0.02013848  0.01368242  0.05141961 -0.03902093
-  0.04681401  0.11661595  0.02467349  0.07719385]</t>
+          <t>[ 0.08872841 -0.01320167  0.03549391  0.00948584  0.09199315 -0.01354269
+ -0.05072576  0.01345282  0.02929437 -0.10438111]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -876,23 +877,24 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.138784217480644</v>
+        <v>4.413195061932108</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[ 0.28137174  0.04667395  0.12437543  0.01916811  0.00986525 -0.11748682
-  0.02830389 -0.05214968  0.02344685  0.02733871]</t>
+          <t>[ 0.08872841 -0.01320167  0.03549391  0.00948584  0.09199315 -0.01354269
+ -0.05072576  0.01345282  0.02929437 -0.10438111]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -900,13 +902,9 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>kjerkoli</t>
@@ -914,7 +912,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -923,31 +921,32 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.138784217480644</v>
+        <v>2.873519599613941</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[ 0.28137174  0.04667395  0.12437543  0.01916811  0.00986525 -0.11748682
-  0.02830389 -0.05214968  0.02344685  0.02733871]</t>
+          <t>[ 0.01185471 -0.00479919 -0.06029232  0.02612571 -0.07023598  0.01478077
+  0.01021861  0.05784628  0.03896456  0.01021511]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
@@ -957,7 +956,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -966,37 +965,38 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.138784217480644</v>
+        <v>2.873519599613941</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[ 0.28137174  0.04667395  0.12437543  0.01916811  0.00986525 -0.11748682
-  0.02830389 -0.05214968  0.02344685  0.02733871]</t>
+          <t>[ 0.01185471 -0.00479919 -0.06029232  0.02612571 -0.07023598  0.01478077
+  0.01021861  0.05784628  0.03896456  0.01021511]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1005,36 +1005,46 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.926386627504079</v>
+        <v>2.873519599613941</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.01185471 -0.00479919 -0.06029232  0.02612571 -0.07023598  0.01478077
+  0.01021861  0.05784628  0.03896456  0.01021511]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1043,22 +1053,24 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3.926386627504079</v>
+        <v>2.873519599613941</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.01185471 -0.00479919 -0.06029232  0.02612571 -0.07023598  0.01478077
+  0.01021861  0.05784628  0.03896456  0.01021511]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1066,17 +1078,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1085,40 +1093,38 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.926386627504079</v>
+        <v>2.873519599613941</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.01185471 -0.00479919 -0.06029232  0.02612571 -0.07023598  0.01478077
+  0.01021861  0.05784628  0.03896456  0.01021511]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1127,36 +1133,38 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.163452673244016</v>
+        <v>4.138784217480644</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.07019132  0.14918076  0.04239488 -0.01734167  0.03742947 -0.17080601
+  0.18663796 -0.20282518 -0.10931357 -0.06602105]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1165,22 +1173,24 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.163452673244016</v>
+        <v>4.138784217480644</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.07019132  0.14918076  0.04239488 -0.01734167  0.03742947 -0.17080601
+  0.18663796 -0.20282518 -0.10931357 -0.06602105]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1188,13 +1198,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1203,22 +1213,24 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.163452673244016</v>
+        <v>4.138784217480644</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.07019132  0.14918076  0.04239488 -0.01734167  0.03742947 -0.17080601
+  0.18663796 -0.20282518 -0.10931357 -0.06602105]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1226,13 +1238,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1241,22 +1253,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.736550823116122</v>
+        <v>4.138784217480644</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.07019132  0.14918076  0.04239488 -0.01734167  0.03742947 -0.17080601
+  0.18663796 -0.20282518 -0.10931357 -0.06602105]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1264,7 +1278,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
@@ -1274,7 +1288,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 1.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1283,22 +1297,24 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.736550823116122</v>
+        <v>4.138784217480644</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.07019132  0.14918076  0.04239488 -0.01734167  0.03742947 -0.17080601
+  0.18663796 -0.20282518 -0.10931357 -0.06602105]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1306,17 +1322,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1325,7 +1341,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.736550823116122</v>
+        <v>3.926386627504079</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1334,13 +1350,14 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1348,13 +1365,9 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
@@ -1367,7 +1380,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.734735382133298</v>
+        <v>3.926386627504079</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1376,13 +1389,14 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1390,18 +1404,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -1413,7 +1419,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.734735382133298</v>
+        <v>3.926386627504079</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1422,27 +1428,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
@@ -1455,7 +1458,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3.734735382133298</v>
+        <v>3.926386627504079</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1464,27 +1467,28 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1493,7 +1497,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.859400341536532</v>
+        <v>3.926386627504079</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1502,13 +1506,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1516,17 +1521,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1535,7 +1536,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.859400341536532</v>
+        <v>3.163452673244016</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1544,27 +1545,28 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1573,7 +1575,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.859400341536532</v>
+        <v>3.163452673244016</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1582,31 +1584,28 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1615,7 +1614,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4.413195061932108</v>
+        <v>3.163452673244016</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1624,27 +1623,32 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1653,7 +1657,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.413195061932108</v>
+        <v>3.163452673244016</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1662,13 +1666,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1676,13 +1681,17 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1691,7 +1700,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.413195061932108</v>
+        <v>3.163452673244016</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1700,21 +1709,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
@@ -1724,7 +1734,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1733,7 +1743,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.415010502914933</v>
+        <v>2.736550823116122</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1742,27 +1752,28 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1771,7 +1782,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3.415010502914933</v>
+        <v>2.736550823116122</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1780,13 +1791,14 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1794,13 +1806,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1809,7 +1821,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.415010502914933</v>
+        <v>2.736550823116122</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1818,13 +1830,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1832,13 +1845,17 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1847,7 +1864,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.026483896746197</v>
+        <v>2.736550823116122</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1856,13 +1873,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1870,21 +1888,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1893,7 +1903,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.026483896746197</v>
+        <v>2.736550823116122</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1902,13 +1912,14 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1916,17 +1927,17 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1935,7 +1946,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.026483896746197</v>
+        <v>3.734735382133298</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1944,13 +1955,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1958,7 +1970,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
@@ -1986,13 +1998,14 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2000,9 +2013,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
@@ -2024,28 +2041,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>ob kosilu</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -2066,27 +2088,28 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2095,7 +2118,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.024668455763372</v>
+        <v>3.734735382133298</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2104,13 +2127,14 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2118,10 +2142,14 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -2133,7 +2161,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4.024668455763372</v>
+        <v>2.859400341536532</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2142,21 +2170,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -2171,7 +2200,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.024668455763372</v>
+        <v>2.859400341536532</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2180,21 +2209,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2217,7 +2247,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.346208775964561</v>
+        <v>2.859400341536532</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2226,28 +2256,25 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -2259,7 +2286,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.346208775964561</v>
+        <v>2.859400341536532</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2268,13 +2295,14 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2282,18 +2310,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -2305,7 +2325,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.346208775964561</v>
+        <v>2.859400341536532</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2314,28 +2334,25 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -2356,24 +2373,29 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
@@ -2394,13 +2416,14 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2408,7 +2431,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -2432,13 +2455,14 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2446,13 +2470,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2470,13 +2494,14 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2484,21 +2509,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2516,13 +2533,14 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2530,17 +2548,21 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>ob kosilu</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2549,7 +2571,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.413195061932108</v>
+        <v>3.415010502914933</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2558,13 +2580,14 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2572,13 +2595,17 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2587,7 +2614,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3.734735382133298</v>
+        <v>3.415010502914933</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2596,13 +2623,14 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2610,13 +2638,17 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2625,7 +2657,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3.734735382133298</v>
+        <v>3.415010502914933</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2634,27 +2666,32 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2663,7 +2700,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3.734735382133298</v>
+        <v>3.415010502914933</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2672,27 +2709,28 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2701,7 +2739,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>4.024668455763372</v>
+        <v>3.415010502914933</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2710,13 +2748,14 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2724,13 +2763,17 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2739,7 +2782,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>4.024668455763372</v>
+        <v>3.026483896746197</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2748,27 +2791,28 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2777,7 +2821,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>4.024668455763372</v>
+        <v>3.026483896746197</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2786,31 +2830,28 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act04</t>
+          <t>Ac_AB4_1_Act01</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>ob kosilu</t>
-        </is>
-      </c>
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2819,7 +2860,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.551979279412752</v>
+        <v>3.026483896746197</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2828,21 +2869,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ac_AB4_1_Act01</t>
+          <t>Ac_AB4_1_Act04</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.246448948938322</v>
+        <v>1.244935600576887</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
@@ -2852,7 +2894,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2861,7 +2903,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.551979279412752</v>
+        <v>3.026483896746197</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2870,53 +2912,1723 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
+        <v>31</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 0.0, 'Ac_AB4_8': 1.0}</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>3.026483896746197</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>33</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>33</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>33</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>33</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>33</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>34</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>34</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>34</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>34</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>34</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>37</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>3.346208775964561</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>37</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>3.346208775964561</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>37</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>3.346208775964561</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>37</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>3.346208775964561</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>37</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>3.346208775964561</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>38</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>38</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>38</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>38</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>38</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>41</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>41</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>41</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>41</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>41</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 0.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>4.413195061932108</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>42</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>42</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>42</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>42</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>42</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>3.734735382133298</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>43</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>43</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>43</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>43</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>43</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ob kosilu</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 0.0, 'Ac_AB4_3': 0.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>4.024668455763372</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
         <v>44</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Ac_AB4_1_Act01</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1.246448948938322</v>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>3.551979279412752</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>44</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>3.551979279412752</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>44</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>kjerkoli</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>3.551979279412752</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>44</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act04</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>ob kosilu</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>kjerkoli</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
         <is>
           <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
         <v>3.551979279412752</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0]</t>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>[ 0.0527479   0.01810029  0.00209554  0.04745629 -0.0928514  -0.09357261
+  0.11293742  0.00812359  0.19670065 -0.04682272]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>44</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ac_AB4_1_Act01</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1.244935600576887</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': 1.0, 'Ac_AB4_2': 1.0, 'Ac_AB4_3': 1.0, 'Ac_AB4_4': 0.0, 'Ac_AB4_5': 1.0, 'Ac_AB4_8': 0.0}</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>{'Ac_AB4_1': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 1. pazim na primerno prehrano', 'Ac_AB4_2': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 2. redno se gibljem v naravi (hoja, tek)', 'Ac_AB4_3': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 3. redno telovadim', 'Ac_AB4_4': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 4. redno se ukvarjam s športom - kaj?', 'Ac_AB4_5': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 5. obdelujem vrt', 'Ac_AB4_8': '4. čim poskrbite za krepitev svojega zdravja in ohranjanje telesnih moči?: 8. ne glede na to, ali delam kaj od zgoraj .... zavestno ne skrbim za zdravje'}</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>3.551979279412752</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>[ 0.17492489 -0.01328735  0.02547147  0.05912164  0.04419725  0.14604512
+ -0.09027019  0.30248728 -0.08645041  0.0650518 ]</t>
         </is>
       </c>
     </row>
